--- a/new original/_Dialog/Drama/_tutorial.xlsx
+++ b/new original/_Dialog/Drama/_tutorial.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="559">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1159,6 +1159,12 @@
   <si>
     <t xml:space="preserve">Oh, you didn’t die even once, huh?
 Good, good. Come here, let me give you some head pats!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NERUN2</t>
   </si>
   <si>
     <t xml:space="preserve">nerun_nadenade2</t>
@@ -3481,7 +3487,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K374"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
@@ -3577,7 +3583,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="4" t="s">
         <v>126</v>
       </c>
@@ -3634,7 +3640,7 @@
       </c>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H18" s="1" t="n">
         <v>327</v>
       </c>
@@ -5245,39 +5251,36 @@
       </c>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="4" t="s">
+        <v>295</v>
+      </c>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="H154" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>296</v>
-      </c>
+      <c r="I154" s="12"/>
+      <c r="J154" s="10"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
       <c r="H155" s="1" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>297</v>
@@ -5287,26 +5290,28 @@
       </c>
       <c r="K155" s="4"/>
     </row>
-    <row r="156" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
+      <c r="C156" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
       <c r="H156" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="I156" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="J156" s="4" t="s">
+      <c r="J156" s="10" t="s">
         <v>300</v>
       </c>
       <c r="K156" s="4"/>
     </row>
-    <row r="157" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5314,15 +5319,20 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
+      <c r="H157" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="I157" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="K157" s="4"/>
     </row>
     <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
-      <c r="B158" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B158" s="4"/>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -5334,7 +5344,9 @@
     </row>
     <row r="159" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="B159" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -5345,9 +5357,7 @@
       <c r="K159" s="4"/>
     </row>
     <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -5358,26 +5368,21 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4"/>
+    <row r="161" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="I161" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="J161" s="10" t="s">
-        <v>302</v>
-      </c>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5386,12 +5391,12 @@
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="1" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="J162" s="4" t="s">
+      <c r="J162" s="10" t="s">
         <v>304</v>
       </c>
       <c r="K162" s="4"/>
@@ -5405,7 +5410,7 @@
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
       <c r="H163" s="1" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>305</v>
@@ -5424,7 +5429,7 @@
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
       <c r="H164" s="1" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>307</v>
@@ -5434,7 +5439,7 @@
       </c>
       <c r="K164" s="4"/>
     </row>
-    <row r="165" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5443,7 +5448,7 @@
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="1" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>309</v>
@@ -5462,7 +5467,7 @@
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
       <c r="H166" s="1" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>311</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="K166" s="4"/>
     </row>
-    <row r="167" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5481,9 +5486,9 @@
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="I167" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I167" s="12" t="s">
         <v>313</v>
       </c>
       <c r="J167" s="4" t="s">
@@ -5500,7 +5505,7 @@
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="1" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I168" s="14" t="s">
         <v>315</v>
@@ -5510,23 +5515,30 @@
       </c>
       <c r="K168" s="4"/>
     </row>
-    <row r="169" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
-      <c r="B169" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B169" s="4"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
+      <c r="H169" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="I169" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>318</v>
+      </c>
       <c r="K169" s="4"/>
     </row>
     <row r="170" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
+      <c r="B170" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -5537,9 +5549,7 @@
       <c r="K170" s="4"/>
     </row>
     <row r="171" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
@@ -5550,26 +5560,21 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="4"/>
+    <row r="172" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
-      <c r="H172" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="J172" s="10" t="s">
-        <v>318</v>
-      </c>
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5578,7 +5583,7 @@
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="1" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I173" s="12" t="s">
         <v>319</v>
@@ -5597,7 +5602,7 @@
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="1" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>321</v>
@@ -5607,7 +5612,7 @@
       </c>
       <c r="K174" s="4"/>
     </row>
-    <row r="175" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5616,7 +5621,7 @@
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="1" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I175" s="12" t="s">
         <v>323</v>
@@ -5626,7 +5631,7 @@
       </c>
       <c r="K175" s="4"/>
     </row>
-    <row r="176" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5635,7 +5640,7 @@
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="1" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I176" s="12" t="s">
         <v>325</v>
@@ -5645,7 +5650,7 @@
       </c>
       <c r="K176" s="4"/>
     </row>
-    <row r="177" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5654,7 +5659,7 @@
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="1" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I177" s="12" t="s">
         <v>327</v>
@@ -5664,25 +5669,30 @@
       </c>
       <c r="K177" s="4"/>
     </row>
-    <row r="178" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
-      <c r="B178" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B178" s="4"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
+      <c r="H178" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="J178" s="10" t="s">
+        <v>330</v>
+      </c>
       <c r="K178" s="4"/>
     </row>
     <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B179" s="4"/>
+      <c r="A179" s="4"/>
+      <c r="B179" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -5692,26 +5702,21 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="4"/>
+    <row r="180" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
-      <c r="H180" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="J180" s="10" t="s">
-        <v>330</v>
-      </c>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5720,12 +5725,12 @@
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="1" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="J181" s="4" t="s">
+      <c r="J181" s="10" t="s">
         <v>332</v>
       </c>
       <c r="K181" s="4"/>
@@ -5739,7 +5744,7 @@
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="1" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>333</v>
@@ -5758,7 +5763,7 @@
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="1" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>335</v>
@@ -5768,7 +5773,7 @@
       </c>
       <c r="K183" s="4"/>
     </row>
-    <row r="184" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5777,7 +5782,7 @@
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="1" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>337</v>
@@ -5787,7 +5792,7 @@
       </c>
       <c r="K184" s="4"/>
     </row>
-    <row r="185" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5795,8 +5800,15 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
+      <c r="H185" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="K185" s="4"/>
     </row>
     <row r="186" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5813,9 +5825,7 @@
     </row>
     <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
-      <c r="B187" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B187" s="4"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -5826,10 +5836,10 @@
       <c r="K187" s="4"/>
     </row>
     <row r="188" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B188" s="4"/>
+      <c r="A188" s="4"/>
+      <c r="B188" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -5840,22 +5850,17 @@
       <c r="K188" s="4"/>
     </row>
     <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="4"/>
+      <c r="A189" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="I189" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="J189" s="10" t="s">
-        <v>340</v>
-      </c>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
       <c r="K189" s="4"/>
     </row>
     <row r="190" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5867,17 +5872,17 @@
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
       <c r="H190" s="1" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="J190" s="4" t="s">
+      <c r="J190" s="10" t="s">
         <v>342</v>
       </c>
       <c r="K190" s="4"/>
     </row>
-    <row r="191" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5886,7 +5891,7 @@
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="1" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I191" s="4" t="s">
         <v>343</v>
@@ -5905,7 +5910,7 @@
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="1" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>345</v>
@@ -5915,7 +5920,7 @@
       </c>
       <c r="K192" s="4"/>
     </row>
-    <row r="193" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5924,7 +5929,7 @@
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="1" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>347</v>
@@ -5934,7 +5939,7 @@
       </c>
       <c r="K193" s="4"/>
     </row>
-    <row r="194" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5943,7 +5948,7 @@
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
       <c r="H194" s="1" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>349</v>
@@ -5953,7 +5958,7 @@
       </c>
       <c r="K194" s="4"/>
     </row>
-    <row r="195" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5962,7 +5967,7 @@
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>351</v>
@@ -5972,54 +5977,62 @@
       </c>
       <c r="K195" s="4"/>
     </row>
-    <row r="196" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
-      <c r="B196" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B196" s="4"/>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
+      <c r="H196" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="K196" s="4"/>
     </row>
     <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="4"/>
+      <c r="A197" s="4"/>
+      <c r="B197" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
     </row>
     <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="4" t="s">
+      <c r="B198" s="4"/>
+    </row>
+    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H200" s="1" t="n">
+    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="201" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H201" s="1" t="n">
         <v>105</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="J200" s="10" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="201" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H201" s="1" t="n">
-        <v>106</v>
       </c>
       <c r="I201" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="J201" s="4" t="s">
+      <c r="J201" s="10" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="202" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H202" s="1" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I202" s="4" t="s">
         <v>357</v>
@@ -6030,7 +6043,7 @@
     </row>
     <row r="203" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H203" s="1" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I203" s="4" t="s">
         <v>359</v>
@@ -6039,9 +6052,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="204" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H204" s="1" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I204" s="4" t="s">
         <v>361</v>
@@ -6050,31 +6063,31 @@
         <v>362</v>
       </c>
     </row>
-    <row r="205" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="4" t="s">
+    <row r="205" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H205" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="J205" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="4" t="s">
+    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H208" s="1" t="n">
+    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="209" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H209" s="1" t="n">
         <v>110</v>
-      </c>
-      <c r="I208" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="J208" s="10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="209" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H209" s="1" t="n">
-        <v>111</v>
       </c>
       <c r="I209" s="4" t="s">
         <v>365</v>
@@ -6085,7 +6098,7 @@
     </row>
     <row r="210" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H210" s="1" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>367</v>
@@ -6094,9 +6107,9 @@
         <v>368</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H211" s="1" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>369</v>
@@ -6105,9 +6118,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="212" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H212" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>371</v>
@@ -6116,9 +6129,9 @@
         <v>372</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H213" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>373</v>
@@ -6126,47 +6139,47 @@
       <c r="J213" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="K213" s="1"/>
-    </row>
-    <row r="214" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="4" t="s">
+    </row>
+    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H214" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="J214" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="K214" s="1"/>
+    </row>
+    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B215" s="4"/>
-    </row>
-    <row r="216" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="4" t="s">
+    <row r="216" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="4"/>
+    </row>
+    <row r="217" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="217" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H218" s="1" t="n">
+    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H219" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="I218" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="J218" s="10" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="219" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H219" s="1" t="n">
-        <v>27</v>
       </c>
       <c r="I219" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="J219" s="4" t="s">
+      <c r="J219" s="10" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="220" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H220" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>379</v>
@@ -6175,9 +6188,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="221" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H221" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I221" s="4" t="s">
         <v>381</v>
@@ -6186,9 +6199,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="222" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H222" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>383</v>
@@ -6197,9 +6210,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="223" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H223" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I223" s="4" t="s">
         <v>385</v>
@@ -6210,29 +6223,29 @@
     </row>
     <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H224" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H225" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="I224" s="4" t="s">
+      <c r="I225" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J224" s="4" t="s">
+      <c r="J225" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H225" s="1" t="n">
+    <row r="226" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H226" s="1" t="n">
         <v>33</v>
-      </c>
-      <c r="I225" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="J225" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H226" s="1" t="n">
-        <v>34</v>
       </c>
       <c r="I226" s="4" t="s">
         <v>389</v>
@@ -6240,92 +6253,92 @@
       <c r="J226" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="K226" s="1"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B227" s="4" t="s">
+      <c r="H227" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="J227" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="K227" s="1"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B228" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K227" s="1"/>
-    </row>
-    <row r="228" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="K228" s="1"/>
+    </row>
     <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="230" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
+    <row r="231" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H233" s="1" t="n">
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H234" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="I233" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="J233" s="10" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="1" t="s">
+      <c r="I234" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="J234" s="10" t="s">
         <v>394</v>
-      </c>
-      <c r="H234" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="I234" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="J234" s="10" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H235" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I235" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H235" s="1" t="n">
+      <c r="J235" s="10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H236" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="I235" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="J235" s="10" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I236" s="4"/>
-      <c r="J236" s="10"/>
+      <c r="I236" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="J236" s="10" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H238" s="1" t="n">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I238" s="4"/>
+      <c r="J238" s="10"/>
+    </row>
+    <row r="239" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H239" s="1" t="n">
         <v>38</v>
-      </c>
-      <c r="I238" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="J238" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="239" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H239" s="1" t="n">
-        <v>39</v>
       </c>
       <c r="I239" s="4" t="s">
         <v>402</v>
@@ -6334,9 +6347,9 @@
         <v>403</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H240" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I240" s="4" t="s">
         <v>404</v>
@@ -6347,7 +6360,7 @@
     </row>
     <row r="241" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H241" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I241" s="4" t="s">
         <v>406</v>
@@ -6355,11 +6368,10 @@
       <c r="J241" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="K241" s="1"/>
     </row>
     <row r="242" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H242" s="1" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I242" s="4" t="s">
         <v>408</v>
@@ -6367,10 +6379,11 @@
       <c r="J242" s="4" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K242" s="1"/>
+    </row>
+    <row r="243" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H243" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I243" s="4" t="s">
         <v>410</v>
@@ -6379,65 +6392,65 @@
         <v>411</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="1" t="s">
+    <row r="244" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H244" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="J244" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J244" s="4"/>
-    </row>
-    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="J245" s="4"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H246" s="1" t="n">
+      <c r="A246" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J246" s="4"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H247" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="I246" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="J246" s="10" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="247" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B247" s="1" t="s">
+      <c r="I247" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J247" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="4" t="s">
+    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="250" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="250" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H250" s="1" t="n">
+    <row r="251" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H251" s="1" t="n">
         <v>93</v>
-      </c>
-      <c r="I250" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="J250" s="10" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="251" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H251" s="1" t="n">
-        <v>94</v>
       </c>
       <c r="I251" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="J251" s="4" t="s">
+      <c r="J251" s="10" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H252" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I252" s="4" t="s">
         <v>418</v>
@@ -6448,7 +6461,7 @@
     </row>
     <row r="253" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H253" s="1" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I253" s="4" t="s">
         <v>420</v>
@@ -6457,31 +6470,31 @@
         <v>421</v>
       </c>
     </row>
-    <row r="254" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H254" s="1" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I254" s="4" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>127</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H255" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J255" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H256" s="1" t="n">
         <v>98</v>
-      </c>
-      <c r="I255" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="J255" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="256" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H256" s="1" t="n">
-        <v>99</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>424</v>
@@ -6490,45 +6503,45 @@
         <v>425</v>
       </c>
     </row>
-    <row r="257" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
+    <row r="257" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H257" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="I257" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="J257" s="4" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B258" s="4" t="s">
+      <c r="I258" s="4"/>
+      <c r="J258" s="4"/>
+    </row>
+    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B259" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="4" t="s">
+    <row r="260" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H260" s="1" t="n">
+    <row r="261" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H261" s="1" t="n">
         <v>100</v>
-      </c>
-      <c r="I260" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="J260" s="10" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="261" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H261" s="1" t="n">
-        <v>101</v>
       </c>
       <c r="I261" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="J261" s="4" t="s">
+      <c r="J261" s="10" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="262" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H262" s="1" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I262" s="4" t="s">
         <v>430</v>
@@ -6537,9 +6550,9 @@
         <v>431</v>
       </c>
     </row>
-    <row r="263" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H263" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I263" s="4" t="s">
         <v>432</v>
@@ -6548,9 +6561,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="264" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H264" s="1" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I264" s="4" t="s">
         <v>434</v>
@@ -6560,47 +6573,47 @@
       </c>
     </row>
     <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I265" s="4"/>
-      <c r="J265" s="4"/>
+      <c r="H265" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="J265" s="4" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B266" s="4" t="s">
+      <c r="I266" s="4"/>
+      <c r="J266" s="4"/>
+    </row>
+    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B267" s="4"/>
-    </row>
     <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="4" t="s">
+      <c r="B268" s="4"/>
+    </row>
+    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H269" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="I269" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J269" s="10" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H270" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J270" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H271" s="1" t="n">
         <v>80</v>
-      </c>
-      <c r="I270" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="271" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H271" s="1" t="n">
-        <v>81</v>
       </c>
       <c r="I271" s="4" t="s">
         <v>438</v>
@@ -6609,9 +6622,9 @@
         <v>439</v>
       </c>
     </row>
-    <row r="272" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H272" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I272" s="4" t="s">
         <v>440</v>
@@ -6620,9 +6633,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="273" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H273" s="1" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I273" s="4" t="s">
         <v>442</v>
@@ -6631,9 +6644,9 @@
         <v>443</v>
       </c>
     </row>
-    <row r="274" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H274" s="1" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I274" s="4" t="s">
         <v>444</v>
@@ -6642,54 +6655,53 @@
         <v>445</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I275" s="4"/>
-      <c r="J275" s="4"/>
-      <c r="K275" s="1"/>
+    <row r="275" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H275" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="I275" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="J275" s="4" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B276" s="4" t="s">
+      <c r="I276" s="4"/>
+      <c r="J276" s="4"/>
+      <c r="K276" s="1"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B277" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K276" s="1"/>
-    </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="4"/>
       <c r="K277" s="1"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="4" t="s">
+      <c r="B278" s="4"/>
+      <c r="K278" s="1"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K278" s="1"/>
-    </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H279" s="1" t="n">
+      <c r="K279" s="1"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H280" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I279" s="4" t="s">
+      <c r="I280" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J279" s="10" t="s">
+      <c r="J280" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="K279" s="1"/>
-    </row>
-    <row r="280" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H280" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="I280" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="J280" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="K280" s="1"/>
     </row>
     <row r="281" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H281" s="1" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I281" s="4" t="s">
         <v>448</v>
@@ -6699,9 +6711,9 @@
       </c>
       <c r="K281" s="1"/>
     </row>
-    <row r="282" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H282" s="1" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I282" s="4" t="s">
         <v>450</v>
@@ -6711,9 +6723,9 @@
       </c>
       <c r="K282" s="1"/>
     </row>
-    <row r="283" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H283" s="1" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I283" s="4" t="s">
         <v>452</v>
@@ -6723,9 +6735,9 @@
       </c>
       <c r="K283" s="1"/>
     </row>
-    <row r="284" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H284" s="1" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I284" s="4" t="s">
         <v>454</v>
@@ -6737,7 +6749,7 @@
     </row>
     <row r="285" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H285" s="1" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I285" s="4" t="s">
         <v>456</v>
@@ -6747,57 +6759,57 @@
       </c>
       <c r="K285" s="1"/>
     </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H286" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="I286" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="J286" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="K286" s="1"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H287" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="I286" s="4" t="s">
+      <c r="I287" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J286" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="K286" s="1"/>
-    </row>
-    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B287" s="4" t="s">
+      <c r="J287" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="K287" s="1"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B288" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K287" s="1"/>
-    </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="4" t="s">
+      <c r="K288" s="1"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="K289" s="1"/>
-    </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H290" s="1" t="n">
+      <c r="K290" s="1"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H291" s="1" t="n">
         <v>74</v>
-      </c>
-      <c r="I290" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="J290" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K290" s="1"/>
-    </row>
-    <row r="291" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H291" s="1" t="n">
-        <v>75</v>
       </c>
       <c r="I291" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="J291" s="4" t="s">
+      <c r="J291" s="10" t="s">
         <v>462</v>
       </c>
       <c r="K291" s="1"/>
     </row>
-    <row r="292" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H292" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I292" s="4" t="s">
         <v>463</v>
@@ -6807,9 +6819,9 @@
       </c>
       <c r="K292" s="1"/>
     </row>
-    <row r="293" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H293" s="1" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I293" s="4" t="s">
         <v>465</v>
@@ -6819,9 +6831,9 @@
       </c>
       <c r="K293" s="1"/>
     </row>
-    <row r="294" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H294" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I294" s="4" t="s">
         <v>467</v>
@@ -6831,9 +6843,16 @@
       </c>
       <c r="K294" s="1"/>
     </row>
-    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I295" s="4"/>
-      <c r="J295" s="4"/>
+    <row r="295" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H295" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="I295" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="J295" s="4" t="s">
+        <v>470</v>
+      </c>
       <c r="K295" s="1"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6841,42 +6860,36 @@
       <c r="J296" s="4"/>
       <c r="K296" s="1"/>
     </row>
-    <row r="297" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B297" s="4" t="s">
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I297" s="4"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="1"/>
+    </row>
+    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B298" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="4" t="s">
+    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="300" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="300" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H300" s="1" t="n">
+    <row r="301" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H301" s="1" t="n">
         <v>66</v>
-      </c>
-      <c r="I300" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="J300" s="10" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="301" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H301" s="1" t="n">
-        <v>67</v>
       </c>
       <c r="I301" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="J301" s="4" t="s">
+      <c r="J301" s="10" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="302" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H302" s="1" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I302" s="4" t="s">
         <v>473</v>
@@ -6885,9 +6898,9 @@
         <v>474</v>
       </c>
     </row>
-    <row r="303" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H303" s="1" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I303" s="4" t="s">
         <v>475</v>
@@ -6896,9 +6909,9 @@
         <v>476</v>
       </c>
     </row>
-    <row r="304" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H304" s="1" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I304" s="4" t="s">
         <v>477</v>
@@ -6909,7 +6922,7 @@
     </row>
     <row r="305" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H305" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I305" s="4" t="s">
         <v>479</v>
@@ -6918,9 +6931,9 @@
         <v>480</v>
       </c>
     </row>
-    <row r="306" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H306" s="1" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I306" s="4" t="s">
         <v>481</v>
@@ -6931,7 +6944,7 @@
     </row>
     <row r="307" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H307" s="1" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I307" s="4" t="s">
         <v>483</v>
@@ -6940,41 +6953,41 @@
         <v>484</v>
       </c>
     </row>
-    <row r="308" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B308" s="4" t="s">
+    <row r="308" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H308" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J308" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B309" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="4" t="s">
+    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H310" s="1" t="n">
+    <row r="311" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H311" s="1" t="n">
         <v>60</v>
-      </c>
-      <c r="I310" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="J310" s="10" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="311" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H311" s="1" t="n">
-        <v>61</v>
       </c>
       <c r="I311" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="J311" s="4" t="s">
+      <c r="J311" s="10" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="312" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H312" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I312" s="4" t="s">
         <v>489</v>
@@ -6985,7 +6998,7 @@
     </row>
     <row r="313" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H313" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I313" s="4" t="s">
         <v>491</v>
@@ -6996,7 +7009,7 @@
     </row>
     <row r="314" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H314" s="1" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I314" s="4" t="s">
         <v>493</v>
@@ -7005,9 +7018,9 @@
         <v>494</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H315" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I315" s="4" t="s">
         <v>495</v>
@@ -7015,35 +7028,35 @@
       <c r="J315" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="K315" s="1"/>
-    </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B316" s="4" t="s">
+    </row>
+    <row r="316" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H316" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="J316" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="K316" s="1"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K316" s="1"/>
-    </row>
-    <row r="317" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K317" s="1"/>
+    </row>
     <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="4" t="s">
+    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="320" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="4" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="320" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H320" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="I320" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="J320" s="10" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H321" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I321" s="4" t="s">
         <v>499</v>
@@ -7054,7 +7067,7 @@
     </row>
     <row r="322" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H322" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I322" s="4" t="s">
         <v>501</v>
@@ -7065,7 +7078,7 @@
     </row>
     <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H323" s="1" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I323" s="4" t="s">
         <v>503</v>
@@ -7074,78 +7087,78 @@
         <v>504</v>
       </c>
     </row>
-    <row r="324" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H324" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="I324" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="J324" s="10" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="325" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="I324" s="4" t="s">
+      <c r="I325" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J324" s="4" t="s">
+      <c r="J325" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="325" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H325" s="1" t="n">
+    <row r="326" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="I325" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="J325" s="10" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H326" s="1" t="n">
+      <c r="I326" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="J326" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H327" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="I326" s="4" t="s">
+      <c r="I327" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J326" s="10" t="s">
+      <c r="J327" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K326" s="1"/>
-    </row>
-    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B327" s="4" t="s">
+      <c r="K327" s="1"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K327" s="1"/>
-    </row>
-    <row r="329" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K328" s="1"/>
+    </row>
     <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="4" t="s">
+    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H332" s="1" t="n">
+    <row r="333" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H333" s="1" t="n">
         <v>45</v>
-      </c>
-      <c r="I332" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="J332" s="10" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="333" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H333" s="1" t="n">
-        <v>46</v>
       </c>
       <c r="I333" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="J333" s="4" t="s">
+      <c r="J333" s="10" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="334" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H334" s="1" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I334" s="4" t="s">
         <v>511</v>
@@ -7154,31 +7167,31 @@
         <v>512</v>
       </c>
     </row>
-    <row r="335" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H335" s="1" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I335" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="J335" s="10" t="s">
+      <c r="J335" s="4" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="336" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H336" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I336" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="J336" s="4" t="s">
+      <c r="J336" s="10" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H337" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I337" s="4" t="s">
         <v>517</v>
@@ -7186,35 +7199,35 @@
       <c r="J337" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="K337" s="1"/>
-    </row>
-    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B338" s="4" t="s">
+    </row>
+    <row r="338" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H338" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="J338" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="K338" s="1"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B339" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K338" s="1"/>
-    </row>
-    <row r="339" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="K339" s="1"/>
+    </row>
     <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="4" t="s">
+    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="342" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="342" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H342" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I342" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="J342" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H343" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I343" s="4" t="s">
         <v>521</v>
@@ -7223,9 +7236,9 @@
         <v>522</v>
       </c>
     </row>
-    <row r="344" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H344" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I344" s="4" t="s">
         <v>523</v>
@@ -7234,9 +7247,9 @@
         <v>524</v>
       </c>
     </row>
-    <row r="345" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H345" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I345" s="4" t="s">
         <v>525</v>
@@ -7247,7 +7260,7 @@
     </row>
     <row r="346" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H346" s="1" t="n">
-        <v>212</v>
+        <v>6</v>
       </c>
       <c r="I346" s="4" t="s">
         <v>527</v>
@@ -7256,9 +7269,9 @@
         <v>528</v>
       </c>
     </row>
-    <row r="347" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H347" s="1" t="n">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="I347" s="4" t="s">
         <v>529</v>
@@ -7267,9 +7280,9 @@
         <v>530</v>
       </c>
     </row>
-    <row r="348" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H348" s="1" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I348" s="4" t="s">
         <v>531</v>
@@ -7278,51 +7291,51 @@
         <v>532</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H349" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="J349" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H350" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I349" s="4" t="s">
+      <c r="I350" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J349" s="10" t="s">
+      <c r="J350" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K349" s="1"/>
-    </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B350" s="4" t="s">
+      <c r="K350" s="1"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B351" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K350" s="1"/>
-    </row>
-    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="1" t="s">
+      <c r="K351" s="1"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D353" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H354" s="1" t="n">
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D354" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H355" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I354" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="J354" s="4" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="355" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H355" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>537</v>
@@ -7331,12 +7344,9 @@
         <v>538</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B356" s="1" t="s">
-        <v>138</v>
-      </c>
+    <row r="356" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H356" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I356" s="4" t="s">
         <v>539</v>
@@ -7345,46 +7355,43 @@
         <v>540</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="1" t="s">
+    <row r="357" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B357" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H357" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I357" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="H359" s="1" t="n">
+      <c r="J357" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H360" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I359" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="J359" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B360" s="1" t="s">
+      <c r="I360" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D360" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H360" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I360" s="1" t="s">
+      <c r="J360" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="J360" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B361" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H361" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>547</v>
@@ -7395,66 +7402,83 @@
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B362" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H362" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I362" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D362" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H362" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I362" s="1" t="s">
+      <c r="J362" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="J362" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B363" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H363" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B364" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D363" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H367" s="1" t="n">
+      <c r="D364" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I367" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="J367" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B368" s="1" t="s">
+      <c r="I368" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B369" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H372" s="1" t="n">
+      <c r="A372" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H373" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I372" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="J372" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B373" s="1" t="s">
+      <c r="I373" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="1" t="s">
         <v>138</v>
       </c>
     </row>
